--- a/data-manipulation-scripts/sheets-cleanup/sheets/EIXO BALANÇA - 02_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/EIXO BALANÇA - 02_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -138,36 +138,12 @@
   <si>
     <t>EIXO BALANÇA PEÇA+ XR250 TORNADO</t>
   </si>
-  <si>
-    <t>602883759619</t>
-  </si>
-  <si>
-    <t>EIXO GARFO TRASEIRO IRON POP100-110 184422</t>
-  </si>
-  <si>
-    <t>7894152034876</t>
-  </si>
-  <si>
-    <t>EIXO GARFO TRASEIRO DANIDREA XTZ250/ XTZ150</t>
-  </si>
-  <si>
-    <t>7899468058547</t>
-  </si>
-  <si>
-    <t>ROLAMENT BALANÇA TRILHA XTZ125 2003 A 2014/ XTZ150 2019 A 2023/ XTZ250</t>
-  </si>
-  <si>
-    <t>4896061</t>
-  </si>
-  <si>
-    <t>ROLAMENT BALANÇA NXR125-150-160/ XRE190-300/ XR250</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -179,23 +155,13 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1CD"/>
-        <bgColor rgb="FFB7E1CD"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -204,7 +170,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -219,18 +185,6 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -986,56 +940,28 @@
       <c r="D64" s="3"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C65" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="D65" s="2">
-        <v>38.0</v>
-      </c>
+      <c r="A65" s="4"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C66" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A66" s="4"/>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
       <c r="D66" s="3"/>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C67" s="7">
-        <v>2.0</v>
-      </c>
-      <c r="D67" s="8"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C68" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="D68" s="7">
-        <v>15.0</v>
-      </c>
+      <c r="A68" s="4"/>
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+      <c r="D68" s="3"/>
     </row>
     <row r="69">
       <c r="A69" s="4"/>
@@ -6599,44 +6525,14 @@
       <c r="C995" s="3"/>
       <c r="D995" s="3"/>
     </row>
-    <row r="996">
-      <c r="A996" s="4"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="4"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="4"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="4"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="4"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A1000">
+  <conditionalFormatting sqref="A1:A995">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A7 A9:A1000">
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="A1:A7 A9:A995">
       <formula1>COUNTIF($A:$A,A1)=1</formula1>
     </dataValidation>
   </dataValidations>
